--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N34_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.846066475944393</v>
+        <v>1.112485802340964</v>
       </c>
       <c r="D2" t="n">
-        <v>15.70354241629391</v>
+        <v>2.55182564264776</v>
       </c>
       <c r="E2" t="n">
-        <v>21.88920595146024</v>
+        <v>3.55699596711229</v>
       </c>
       <c r="F2" t="n">
-        <v>9.217941060987373</v>
+        <v>1.497915422410448</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.11468476505568</v>
+        <v>6.031136274321548</v>
       </c>
       <c r="D3" t="n">
-        <v>37.79039513111368</v>
+        <v>6.140939208805973</v>
       </c>
       <c r="E3" t="n">
-        <v>21.88920595146024</v>
+        <v>3.55699596711229</v>
       </c>
       <c r="F3" t="n">
-        <v>9.217941060987373</v>
+        <v>1.497915422410448</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17.64859227243081</v>
+        <v>2.867896244270007</v>
       </c>
       <c r="D4" t="n">
-        <v>18.8379190788352</v>
+        <v>3.061161850310719</v>
       </c>
       <c r="E4" t="n">
-        <v>21.88920595146024</v>
+        <v>3.55699596711229</v>
       </c>
       <c r="F4" t="n">
-        <v>9.217941060987373</v>
+        <v>1.497915422410448</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.82739779031273</v>
+        <v>2.246952140925818</v>
       </c>
       <c r="D5" t="n">
-        <v>16.38387553002343</v>
+        <v>2.662379773628808</v>
       </c>
       <c r="E5" t="n">
-        <v>21.88920595146024</v>
+        <v>3.55699596711229</v>
       </c>
       <c r="F5" t="n">
-        <v>9.217941060987373</v>
+        <v>1.497915422410448</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.95711769167373</v>
+        <v>6.168031624896981</v>
       </c>
       <c r="D6" t="n">
-        <v>31.28811294596812</v>
+        <v>5.084318353719819</v>
       </c>
       <c r="E6" t="n">
-        <v>21.88920595146024</v>
+        <v>3.55699596711229</v>
       </c>
       <c r="F6" t="n">
-        <v>9.217941060987373</v>
+        <v>1.497915422410448</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>72.62285854786742</v>
+        <v>11.80121451402846</v>
       </c>
       <c r="D7" t="n">
-        <v>35.64795233887138</v>
+        <v>5.7927922550666</v>
       </c>
       <c r="E7" t="n">
-        <v>21.88920595146024</v>
+        <v>3.55699596711229</v>
       </c>
       <c r="F7" t="n">
-        <v>9.217941060987373</v>
+        <v>1.497915422410448</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
